--- a/docs/folha-modelo/diario-de-bordo-v3.xlsx
+++ b/docs/folha-modelo/diario-de-bordo-v3.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Exemplo (verso)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Frente'!$A$1:$R$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Verso'!$A$1:$R$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Exemplo (frente)'!$A$1:$R$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Exemplo (verso)'!$A$1:$R$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Frente'!$A$1:$S$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Verso'!$A$1:$S$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Exemplo (frente)'!$A$1:$S$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Exemplo (verso)'!$A$1:$S$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,8 @@
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
     <col width="7.5" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -688,6 +689,7 @@
         </is>
       </c>
       <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -708,6 +710,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -752,6 +755,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -780,6 +784,7 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -838,6 +843,12 @@
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>CONTINUA
+A PEÇA Nº</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -910,6 +921,7 @@
       </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="15" t="n">
@@ -931,7 +943,8 @@
       <c r="O7" s="17" t="n"/>
       <c r="P7" s="17" t="n"/>
       <c r="Q7" s="18" t="n"/>
-      <c r="R7" s="19" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="19" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="15" t="n">
@@ -953,7 +966,8 @@
       <c r="O8" s="17" t="n"/>
       <c r="P8" s="17" t="n"/>
       <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="19" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="19" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="15" t="n">
@@ -975,7 +989,8 @@
       <c r="O9" s="17" t="n"/>
       <c r="P9" s="17" t="n"/>
       <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="19" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="19" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="15" t="n">
@@ -997,7 +1012,8 @@
       <c r="O10" s="17" t="n"/>
       <c r="P10" s="17" t="n"/>
       <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="19" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="19" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="15" t="n">
@@ -1019,7 +1035,8 @@
       <c r="O11" s="17" t="n"/>
       <c r="P11" s="17" t="n"/>
       <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="19" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="19" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="15" t="n">
@@ -1041,7 +1058,8 @@
       <c r="O12" s="17" t="n"/>
       <c r="P12" s="17" t="n"/>
       <c r="Q12" s="18" t="n"/>
-      <c r="R12" s="19" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="19" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="n">
@@ -1063,7 +1081,8 @@
       <c r="O13" s="17" t="n"/>
       <c r="P13" s="17" t="n"/>
       <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="19" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="19" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="15" t="n">
@@ -1085,7 +1104,8 @@
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
       <c r="Q14" s="18" t="n"/>
-      <c r="R14" s="19" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="19" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="n">
@@ -1107,7 +1127,8 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="17" t="n"/>
       <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="19" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="19" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="15" t="n">
@@ -1129,120 +1150,124 @@
       <c r="O16" s="17" t="n"/>
       <c r="P16" s="17" t="n"/>
       <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="19" t="n"/>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="17" t="n"/>
-      <c r="M17" s="17" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="17" t="n"/>
-      <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="18" t="n"/>
-      <c r="R17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>2. PARADAS DA MÁQUINA</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>escreva o Nº da peça que estava na máquina (ou “—” se não havia peça)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Nº DA
+PEÇA
+(ou —)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>CHAPA</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>INÍCIO</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>FIM</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="n"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>escreva o Nº da peça que estava na máquina (ou “—” se não havia peça)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>TURNO</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>MOTIVO
+(código 1–11)</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>DESCRIÇÃO DA PARADA</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Nº DA
-PEÇA
-(ou —)</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>CHAPA</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>INÍCIO</t>
-        </is>
-      </c>
+      <c r="S18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="17" t="n"/>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>FIM</t>
-        </is>
-      </c>
+      <c r="G19" s="17" t="n"/>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>TURNO</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>MOTIVO
-(código 1–11)</t>
-        </is>
-      </c>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO DA PARADA</t>
-        </is>
-      </c>
+      <c r="L19" s="19" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
@@ -1261,10 +1286,11 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -1283,10 +1309,11 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -1305,10 +1332,11 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -1327,10 +1355,11 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -1349,10 +1378,11 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -1371,10 +1401,11 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
@@ -1393,10 +1424,11 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -1415,566 +1447,635 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>COMO PREENCHER</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="17" t="n"/>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>CÓDIGOS DE PARADA (coluna MOTIVO)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
       <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>EXEMPLO: VIGA D51, 13:00 ÀS 17:00, PAROU 14:30–15:30</t>
-        </is>
-      </c>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">1. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Uma linha = uma peça.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> Começou peça nova? Linha nova.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">2. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Trecho</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> = tempo produzindo, </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>sem parada no meio</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">. Parou a máquina? </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Feche o trecho</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> (FIM).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">3. Anote a parada no </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>quadro 2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">, com o </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Nº da peça</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> e o código do motivo.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">4. Voltou a produzir a mesma peça? Use o </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>próximo trecho da mesma linha</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">5. Troca de turno no meio da peça: o próximo operador usa o próximo trecho, com a chapa dele.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">6. Marque </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>✓ PRONTA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> quando a peça terminar. Não terminou? Deixe em branco e continue na próxima folha.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="22" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Mecânica
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Elétrica
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Preventiva
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Aguardando peça
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Falta de peça
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>6</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Ponte rolante</t>
-          </r>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="22" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Troca de consumíveis
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Troca de peça
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>9</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Set-up
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>10</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Tyorei
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Outros</t>
-          </r>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="21" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Quadro 1 (peça 1): </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · ✓
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Quadro 2: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Nº da peça 1 · 14:30–15:30 · motivo 4 (aguardando peça)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Certo: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">3 h de produção + 1 h parada = 4 h.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Errado: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>um trecho 13:00–17:00 com a parada dentro dele (a hora parada conta duas vezes).</t>
-          </r>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>COMO PREENCHER</t>
+        </is>
+      </c>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>CÓDIGOS DE PARADA (coluna MOTIVO)</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="20" t="inlineStr">
+        <is>
+          <t>EXEMPLO: VIGA D51, 13:00 ÀS 17:00, PAROU 14:30–15:30</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="2" t="n"/>
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Uma linha = uma peça.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Começou peça nova? Linha nova.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Trecho</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> = tempo produzindo, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>sem parada no meio</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">. Parou a máquina? </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Feche o trecho</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> (FIM).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3. Anote a parada no </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>quadro 2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">, com o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Nº da peça</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> e o código do motivo.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">4. Voltou a produzir a mesma peça? Use o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>próximo trecho da mesma linha</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">5. Troca de turno no meio da peça: o próximo operador usa o próximo trecho, com a chapa dele.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">6. Marque </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>✓ PRONTA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> quando a peça terminar. Não terminou? Deixe em branco e continue na próxima folha.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">7. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Mais de 4 trechos na mesma peça?</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Continue na </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>linha de baixo</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">, com a mesma peça, e escreva em </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>CONTINUA A PEÇA Nº</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> o número da linha de cima. ✓ só na última linha.</t>
+          </r>
+        </is>
+      </c>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Mecânica
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Elétrica
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Preventiva
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Aguardando peça
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Falta de peça
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Ponte rolante</t>
+          </r>
+        </is>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Troca de consumíveis
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Troca de peça
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Set-up
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Tyorei
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Outros</t>
+          </r>
+        </is>
+      </c>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Quadro 1 (peça 1): </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · ✓
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Quadro 2: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Nº da peça 1 · 14:30–15:30 · motivo 4 (aguardando peça)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Certo: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3 h de produção + 1 h parada = 4 h.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Errado: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>um trecho 13:00–17:00 com a parada dentro dele (a hora parada conta duas vezes).</t>
+          </r>
+        </is>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="2" t="n"/>
@@ -1995,6 +2096,7 @@
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="2" t="n"/>
@@ -2015,6 +2117,7 @@
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="2" t="n"/>
@@ -2035,6 +2138,7 @@
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
       <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="2" t="n"/>
@@ -2055,79 +2159,135 @@
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="83">
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="L25:R25"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="H29:L29"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="L22:R22"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I4:R4"/>
-    <mergeCell ref="N5:P5"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="L21:R21"/>
     <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="L24:S24"/>
+    <mergeCell ref="L18:S18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="K32:L38"/>
+    <mergeCell ref="H32:J38"/>
+    <mergeCell ref="L26:S26"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="L27:S27"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="L19:S19"/>
     <mergeCell ref="M1:N1"/>
+    <mergeCell ref="L28:S28"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L23:S23"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="M31:S31"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A32:G38"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="N3:O3"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="J24:K24"/>
+    <mergeCell ref="M32:S38"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L20:S20"/>
+    <mergeCell ref="L29:S29"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="L21:S21"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A1:L2"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="K30:L36"/>
-    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M29:R29"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="M30:R36"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="L25:S25"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="L24:R24"/>
-    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="I4:S4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="J18:K18"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L23:R23"/>
-    <mergeCell ref="A30:G36"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="H30:J36"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="L20:R20"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0" footer="0"/>
@@ -2141,7 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2161,7 +2321,8 @@
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
     <col width="7.5" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2215,6 +2376,7 @@
         </is>
       </c>
       <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -2235,6 +2397,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -2263,6 +2426,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -2321,6 +2485,12 @@
         </is>
       </c>
       <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>CONTINUA
+A PEÇA Nº</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -2393,10 +2563,11 @@
       </c>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -2414,11 +2585,12 @@
       <c r="O6" s="17" t="n"/>
       <c r="P6" s="17" t="n"/>
       <c r="Q6" s="18" t="n"/>
-      <c r="R6" s="19" t="n"/>
+      <c r="R6" s="7" t="n"/>
+      <c r="S6" s="19" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -2436,11 +2608,12 @@
       <c r="O7" s="17" t="n"/>
       <c r="P7" s="17" t="n"/>
       <c r="Q7" s="18" t="n"/>
-      <c r="R7" s="19" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="19" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -2458,11 +2631,12 @@
       <c r="O8" s="17" t="n"/>
       <c r="P8" s="17" t="n"/>
       <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="19" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="19" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
@@ -2480,11 +2654,12 @@
       <c r="O9" s="17" t="n"/>
       <c r="P9" s="17" t="n"/>
       <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="19" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="19" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -2502,11 +2677,12 @@
       <c r="O10" s="17" t="n"/>
       <c r="P10" s="17" t="n"/>
       <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="19" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="19" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -2524,11 +2700,12 @@
       <c r="O11" s="17" t="n"/>
       <c r="P11" s="17" t="n"/>
       <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="19" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="19" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -2546,11 +2723,12 @@
       <c r="O12" s="17" t="n"/>
       <c r="P12" s="17" t="n"/>
       <c r="Q12" s="18" t="n"/>
-      <c r="R12" s="19" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="19" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -2568,11 +2746,12 @@
       <c r="O13" s="17" t="n"/>
       <c r="P13" s="17" t="n"/>
       <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="19" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="19" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -2590,11 +2769,12 @@
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
       <c r="Q14" s="18" t="n"/>
-      <c r="R14" s="19" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="19" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -2612,11 +2792,12 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="17" t="n"/>
       <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="19" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="19" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -2634,11 +2815,12 @@
       <c r="O16" s="17" t="n"/>
       <c r="P16" s="17" t="n"/>
       <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="19" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="19" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -2656,120 +2838,124 @@
       <c r="O17" s="17" t="n"/>
       <c r="P17" s="17" t="n"/>
       <c r="Q17" s="18" t="n"/>
-      <c r="R17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="17" t="n"/>
+      <c r="P18" s="17" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2. PARADAS (continuação)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Nº da peça que estava na máquina, ou “—”</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Nº DA
-PEÇA
-(ou —)</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>CHAPA</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>INÍCIO</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>FIM</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>TURNO</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>MOTIVO
-(código 1–11)</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO DA PARADA</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="S19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Nº DA
+PEÇA
+(ou —)</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>CHAPA</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>INÍCIO</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="17" t="n"/>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>FIM</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>TURNO</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>MOTIVO
+(código 1–11)</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="19" t="n"/>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>DESCRIÇÃO DA PARADA</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -2788,10 +2974,11 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -2810,10 +2997,11 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -2832,10 +3020,11 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -2854,10 +3043,11 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -2876,10 +3066,11 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
@@ -2898,10 +3089,11 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -2920,10 +3112,11 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -2942,10 +3135,11 @@
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -2964,276 +3158,332 @@
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>FECHAMENTO DA FOLHA (contramestre)</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="17" t="n"/>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>PEÇAS</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
       <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="20" t="inlineStr">
-        <is>
-          <t>LEMBRETE</t>
-        </is>
-      </c>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>Horas produzindo (soma dos trechos)</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="24">
-        <f>SUMPRODUCT(('Frente'!G7:G17&lt;&gt;"")*MOD('Frente'!G7:G17-'Frente'!F7:F17,1))+SUMPRODUCT(('Frente'!J7:J17&lt;&gt;"")*MOD('Frente'!J7:J17-'Frente'!I7:I17,1))+SUMPRODUCT(('Frente'!M7:M17&lt;&gt;"")*MOD('Frente'!M7:M17-'Frente'!L7:L17,1))+SUMPRODUCT(('Frente'!P7:P17&lt;&gt;"")*MOD('Frente'!P7:P17-'Frente'!O7:O17,1))+SUMPRODUCT(('Verso'!G6:G17&lt;&gt;"")*MOD('Verso'!G6:G17-'Verso'!F6:F17,1))+SUMPRODUCT(('Verso'!J6:J17&lt;&gt;"")*MOD('Verso'!J6:J17-'Verso'!I6:I17,1))+SUMPRODUCT(('Verso'!M6:M17&lt;&gt;"")*MOD('Verso'!M6:M17-'Verso'!L6:L17,1))+SUMPRODUCT(('Verso'!P6:P17&lt;&gt;"")*MOD('Verso'!P6:P17-'Verso'!O6:O17,1))</f>
-        <v/>
-      </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="23" t="inlineStr">
-        <is>
-          <t>Peças prontas (nº de ✓)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="18">
-        <f>COUNTA('Frente'!Q7:Q17)+COUNTA('Verso'!Q6:Q17)</f>
-        <v/>
-      </c>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Trecho é só produção.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> Parou? Feche o trecho e anote a parada com o </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Nº da peça</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">. Voltou? </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Próximo trecho da mesma linha</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>. ✓ quando a peça ficar pronta.</t>
-          </r>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>Horas paradas (soma do quadro 2)</t>
+      <c r="S31" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>FECHAMENTO DA FOLHA (contramestre)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
-      <c r="E33" s="24">
-        <f>SUMPRODUCT(('Frente'!G20:G27&lt;&gt;"")*MOD('Frente'!G20:G27-'Frente'!E20:E27,1))+SUMPRODUCT(('Verso'!G20:G29&lt;&gt;"")*MOD('Verso'!G20:G29-'Verso'!E20:E29,1))</f>
-        <v/>
-      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t>Continuam na próxima folha</t>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>PEÇAS</t>
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
-      <c r="K33" s="18">
-        <f>SUMPRODUCT(('Frente'!C7:C17&lt;&gt;"")*('Frente'!Q7:Q17=""))+SUMPRODUCT(('Verso'!C6:C17&lt;&gt;"")*('Verso'!Q6:Q17=""))</f>
-        <v/>
-      </c>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>LEMBRETE</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Total (24 h no dia, ou as horas dos turnos)</t>
+          <t>Horas produzindo (soma dos trechos)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="24">
-        <f>E32+E33</f>
+        <f>SUMPRODUCT(('Frente'!G7:G16&lt;&gt;"")*MOD('Frente'!G7:G16-'Frente'!F7:F16,1))+SUMPRODUCT(('Frente'!J7:J16&lt;&gt;"")*MOD('Frente'!J7:J16-'Frente'!I7:I16,1))+SUMPRODUCT(('Frente'!M7:M16&lt;&gt;"")*MOD('Frente'!M7:M16-'Frente'!L7:L16,1))+SUMPRODUCT(('Frente'!P7:P16&lt;&gt;"")*MOD('Frente'!P7:P16-'Frente'!O7:O16,1))+SUMPRODUCT(('Verso'!G6:G18&lt;&gt;"")*MOD('Verso'!G6:G18-'Verso'!F6:F18,1))+SUMPRODUCT(('Verso'!J6:J18&lt;&gt;"")*MOD('Verso'!J6:J18-'Verso'!I6:I18,1))+SUMPRODUCT(('Verso'!M6:M18&lt;&gt;"")*MOD('Verso'!M6:M18-'Verso'!L6:L18,1))+SUMPRODUCT(('Verso'!P6:P18&lt;&gt;"")*MOD('Verso'!P6:P18-'Verso'!O6:O18,1))</f>
         <v/>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>Conferido por (chapa)</t>
+          <t>Peças prontas (nº de ✓)</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
-      <c r="K34" s="18" t="n"/>
+      <c r="K34" s="18">
+        <f>COUNTA('Frente'!Q7:Q16)+COUNTA('Verso'!Q6:Q18)</f>
+        <v/>
+      </c>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Trecho é só produção.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Parou? Feche o trecho e anote a parada com o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Nº da peça</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">. Voltou? </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Próximo trecho da mesma linha</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>. ✓ quando a peça ficar pronta.</t>
+          </r>
+        </is>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="21" customHeight="1"/>
-    <row r="36" ht="21" customHeight="1"/>
+      <c r="S34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Horas paradas (soma do quadro 2)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="24">
+        <f>SUMPRODUCT(('Frente'!G19:G29&lt;&gt;"")*MOD('Frente'!G19:G29-'Frente'!E19:E29,1))+SUMPRODUCT(('Verso'!G21:G31&lt;&gt;"")*MOD('Verso'!G21:G31-'Verso'!E21:E31,1))</f>
+        <v/>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>Continuam na próxima folha</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="18">
+        <f>SUMPRODUCT(('Frente'!C7:C16&lt;&gt;"")*('Frente'!Q7:Q16=""))+SUMPRODUCT(('Verso'!C6:C18&lt;&gt;"")*('Verso'!Q6:Q18=""))</f>
+        <v/>
+      </c>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Total (24 h no dia, ou as horas dos turnos)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="24">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>Conferido por (chapa)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1"/>
+    <row r="38" ht="21" customHeight="1"/>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="86">
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="M33:S33"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="L21:R21"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="M31:R31"/>
+    <mergeCell ref="K35:L35"/>
     <mergeCell ref="A1:L2"/>
     <mergeCell ref="O1:P1"/>
+    <mergeCell ref="L24:S24"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="L26:S26"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="J31:K31"/>
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="J21:K21"/>
-    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="E35:G35"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="L27:S27"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L20:R20"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="L22:R22"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="L28:S28"/>
     <mergeCell ref="J27:K27"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="L23:S23"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="K4:M4"/>
+    <mergeCell ref="M34:S36"/>
+    <mergeCell ref="H35:J35"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="L24:R24"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="E33:G33"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="H4:J4"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="I3:R3"/>
-    <mergeCell ref="L25:R25"/>
+    <mergeCell ref="I19:S19"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="E36:G36"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="J24:K24"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L28:R28"/>
+    <mergeCell ref="L30:S30"/>
+    <mergeCell ref="L20:S20"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="L29:S29"/>
     <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L23:R23"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="L31:S31"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="L21:S21"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H33:L33"/>
     <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A32:D32"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="R4:R5"/>
+    <mergeCell ref="H36:J36"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="J30:K30"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="G28:H28"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="M32:R34"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="I3:S3"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="L25:S25"/>
+    <mergeCell ref="S4:S5"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -3248,7 +3498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3268,7 +3518,8 @@
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
     <col width="7.5" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3322,6 +3573,7 @@
         </is>
       </c>
       <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -3342,6 +3594,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -3394,6 +3647,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -3422,6 +3676,7 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -3480,6 +3735,12 @@
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>CONTINUA
+A PEÇA Nº</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -3552,6 +3813,7 @@
       </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="15" t="n">
@@ -3597,7 +3859,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R7" s="19" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="19" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="15" t="n">
@@ -3651,7 +3914,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="19" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="19" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="15" t="n">
@@ -3697,7 +3961,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R9" s="19" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="19" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="15" t="n">
@@ -3751,7 +4016,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="19" t="inlineStr">
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="19" t="inlineStr">
         <is>
           <t>Troca de turno no meio da peça</t>
         </is>
@@ -3785,31 +4051,48 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="G11" s="17" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="M11" s="17" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="O11" s="17" t="n">
         <v>0.7847222222222222</v>
       </c>
-      <c r="J11" s="17" t="n">
-        <v>0.8611111111111112</v>
-      </c>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="17" t="n"/>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="17" t="n"/>
-      <c r="P11" s="17" t="n"/>
-      <c r="Q11" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="19" t="n"/>
+      <c r="P11" s="17" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="19" t="inlineStr">
+        <is>
+          <t>4 trechos cheios: segue na linha 6</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="15" t="n">
@@ -3836,10 +4119,10 @@
         </is>
       </c>
       <c r="F12" s="17" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="H12" s="16" t="n"/>
       <c r="I12" s="17" t="n"/>
@@ -3855,7 +4138,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="19" t="n"/>
+      <c r="R12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="19" t="inlineStr">
+        <is>
+          <t>Continuação da peça 5</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="n">
@@ -3863,29 +4153,29 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>16/10</t>
+          <t>15/10</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>BOOM WA</t>
+          <t>LANÇA</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>WA200-6</t>
+          <t>PC360LC-8M2</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.1319444444444444</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="H13" s="16" t="n"/>
       <c r="I13" s="17" t="n"/>
@@ -3901,7 +4191,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="19" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="19" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="15" t="n">
@@ -3928,10 +4219,10 @@
         </is>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.1527777777777778</v>
+        <v>0.01388888888888889</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.25</v>
+        <v>0.1319444444444444</v>
       </c>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="17" t="n"/>
@@ -3942,23 +4233,44 @@
       <c r="N14" s="16" t="n"/>
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="18" t="n"/>
-      <c r="R14" s="19" t="inlineStr">
-        <is>
-          <t>Continua na próxima folha</t>
-        </is>
-      </c>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="19" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>16/10</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>BOOM WA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>WA200-6</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.25</v>
+      </c>
       <c r="H15" s="16" t="n"/>
       <c r="I15" s="17" t="n"/>
       <c r="J15" s="17" t="n"/>
@@ -3969,7 +4281,12 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="17" t="n"/>
       <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="19" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="19" t="inlineStr">
+        <is>
+          <t>Continua na próxima folha</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="15" t="n">
@@ -3991,108 +4308,133 @@
       <c r="O16" s="17" t="n"/>
       <c r="P16" s="17" t="n"/>
       <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="19" t="n"/>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="17" t="n"/>
-      <c r="M17" s="17" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="17" t="n"/>
-      <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="18" t="n"/>
-      <c r="R17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>2. PARADAS DA MÁQUINA</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>escreva o Nº da peça que estava na máquina (ou “—” se não havia peça)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Nº DA
+PEÇA
+(ou —)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>CHAPA</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>INÍCIO</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>FIM</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="n"/>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>escreva o Nº da peça que estava na máquina (ou “—” se não havia peça)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>TURNO</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>MOTIVO
+(código 1–11)</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>DESCRIÇÃO DA PARADA</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Nº DA
-PEÇA
-(ou —)</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>CHAPA</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>INÍCIO</t>
-        </is>
+      <c r="S18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>15/10</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0.25</v>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>FIM</t>
-        </is>
+      <c r="G19" s="17" t="n">
+        <v>0.2708333333333333</v>
       </c>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>TURNO</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>MOTIVO
-(código 1–11)</t>
-        </is>
+      <c r="I19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO DA PARADA</t>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>Set-up do dispositivo da lança</t>
         </is>
       </c>
       <c r="M19" s="2" t="n"/>
@@ -4101,13 +4443,14 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -4120,23 +4463,23 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.25</v>
+        <v>0.40625</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="17" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.4305555555555556</v>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="19" t="inlineStr">
         <is>
-          <t>Set-up do dispositivo da lança</t>
+          <t>Troca de bico e arame</t>
         </is>
       </c>
       <c r="M20" s="2" t="n"/>
@@ -4145,13 +4488,14 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -4164,23 +4508,23 @@
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>0.40625</v>
+        <v>0.4618055555555556</v>
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="17" t="n">
-        <v>0.4305555555555556</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="19" t="inlineStr">
         <is>
-          <t>Troca de bico e arame</t>
+          <t>Ponte ocupada no setor</t>
         </is>
       </c>
       <c r="M21" s="2" t="n"/>
@@ -4189,13 +4533,16 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -4204,27 +4551,27 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.4618055555555556</v>
+        <v>0.6423611111111112</v>
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="17" t="n">
-        <v>0.4930555555555556</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="19" t="inlineStr">
         <is>
-          <t>Ponte ocupada no setor</t>
+          <t>Sem peça no setor</t>
         </is>
       </c>
       <c r="M22" s="2" t="n"/>
@@ -4233,15 +4580,14 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -4254,23 +4600,23 @@
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0.6423611111111112</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="17" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="19" t="inlineStr">
         <is>
-          <t>Sem peça no setor</t>
+          <t>Troca de bico</t>
         </is>
       </c>
       <c r="M23" s="2" t="n"/>
@@ -4279,10 +4625,11 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>5</v>
@@ -4298,34 +4645,39 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="17" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.7569444444444444</v>
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="19" t="inlineStr"/>
+      <c r="L24" s="19" t="inlineStr">
+        <is>
+          <t>Ponte para virar a peça</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -4338,38 +4690,35 @@
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="17" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K25" s="2" t="n"/>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>Tocha travando, mecânico ajustou</t>
-        </is>
-      </c>
+      <c r="L25" s="19" t="inlineStr"/>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -4378,27 +4727,27 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="17" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="19" t="inlineStr">
         <is>
-          <t>Set-up para o boom</t>
+          <t>Tyorei</t>
         </is>
       </c>
       <c r="M26" s="2" t="n"/>
@@ -4407,42 +4756,43 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>16/10</t>
+          <t>15/10</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>0.1319444444444444</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="17" t="n">
-        <v>0.1527777777777778</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="19" t="inlineStr">
         <is>
-          <t>Queda de energia no painel</t>
+          <t>Tocha travando, mecânico ajustou</t>
         </is>
       </c>
       <c r="M27" s="2" t="n"/>
@@ -4451,566 +4801,679 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>COMO PREENCHER</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>15/10</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="17" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>Set-up para o boom</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>16/10</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0.1319444444444444</v>
+      </c>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>CÓDIGOS DE PARADA (coluna MOTIVO)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
+      <c r="G29" s="17" t="n">
+        <v>0.1527777777777778</v>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>EXEMPLO: VIGA D51, 13:00 ÀS 17:00, PAROU 14:30–15:30</t>
-        </is>
-      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>Queda de energia no painel</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">1. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Uma linha = uma peça.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> Começou peça nova? Linha nova.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">2. </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Trecho</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> = tempo produzindo, </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>sem parada no meio</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">. Parou a máquina? </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Feche o trecho</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> (FIM).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">3. Anote a parada no </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>quadro 2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">, com o </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Nº da peça</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> e o código do motivo.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">4. Voltou a produzir a mesma peça? Use o </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>próximo trecho da mesma linha</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">5. Troca de turno no meio da peça: o próximo operador usa o próximo trecho, com a chapa dele.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">6. Marque </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>✓ PRONTA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> quando a peça terminar. Não terminou? Deixe em branco e continue na próxima folha.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="22" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Mecânica
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Elétrica
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>3</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Preventiva
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>4</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Aguardando peça
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Falta de peça
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>6</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Ponte rolante</t>
-          </r>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="22" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Troca de consumíveis
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Troca de peça
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>9</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Set-up
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>10</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Tyorei
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">  Outros</t>
-          </r>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="21" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Quadro 1 (peça 1): </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · ✓
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Quadro 2: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Nº da peça 1 · 14:30–15:30 · motivo 4 (aguardando peça)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Certo: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">3 h de produção + 1 h parada = 4 h.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">Errado: </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>um trecho 13:00–17:00 com a parada dentro dele (a hora parada conta duas vezes).</t>
-          </r>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>COMO PREENCHER</t>
+        </is>
+      </c>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>CÓDIGOS DE PARADA (coluna MOTIVO)</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="20" t="inlineStr">
+        <is>
+          <t>EXEMPLO: VIGA D51, 13:00 ÀS 17:00, PAROU 14:30–15:30</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="2" t="n"/>
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Uma linha = uma peça.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Começou peça nova? Linha nova.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Trecho</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> = tempo produzindo, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>sem parada no meio</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">. Parou a máquina? </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Feche o trecho</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> (FIM).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3. Anote a parada no </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>quadro 2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">, com o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Nº da peça</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> e o código do motivo.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">4. Voltou a produzir a mesma peça? Use o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>próximo trecho da mesma linha</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">5. Troca de turno no meio da peça: o próximo operador usa o próximo trecho, com a chapa dele.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">6. Marque </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>✓ PRONTA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> quando a peça terminar. Não terminou? Deixe em branco e continue na próxima folha.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">7. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Mais de 4 trechos na mesma peça?</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Continue na </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>linha de baixo</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">, com a mesma peça, e escreva em </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>CONTINUA A PEÇA Nº</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> o número da linha de cima. ✓ só na última linha.</t>
+          </r>
+        </is>
+      </c>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Mecânica
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Elétrica
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Preventiva
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Aguardando peça
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Falta de peça
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Ponte rolante</t>
+          </r>
+        </is>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Troca de consumíveis
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Troca de peça
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Set-up
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Tyorei
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">  Outros</t>
+          </r>
+        </is>
+      </c>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Quadro 1 (peça 1): </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · ✓
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Quadro 2: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Nº da peça 1 · 14:30–15:30 · motivo 4 (aguardando peça)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Certo: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">3 h de produção + 1 h parada = 4 h.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">Errado: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>um trecho 13:00–17:00 com a parada dentro dele (a hora parada conta duas vezes).</t>
+          </r>
+        </is>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="2" t="n"/>
@@ -5031,6 +5494,7 @@
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="2" t="n"/>
@@ -5051,6 +5515,7 @@
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="2" t="n"/>
@@ -5071,6 +5536,7 @@
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
       <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="2" t="n"/>
@@ -5091,79 +5557,135 @@
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="83">
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="L25:R25"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="H29:L29"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="L22:R22"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I4:R4"/>
-    <mergeCell ref="N5:P5"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="L21:R21"/>
     <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="L24:S24"/>
+    <mergeCell ref="L18:S18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="K32:L38"/>
+    <mergeCell ref="H32:J38"/>
+    <mergeCell ref="L26:S26"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="L27:S27"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="L19:S19"/>
     <mergeCell ref="M1:N1"/>
+    <mergeCell ref="L28:S28"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L23:S23"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I17:S17"/>
+    <mergeCell ref="M31:S31"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A32:G38"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="N3:O3"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="J24:K24"/>
+    <mergeCell ref="M32:S38"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L20:S20"/>
+    <mergeCell ref="L29:S29"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="L21:S21"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A1:L2"/>
     <mergeCell ref="G19:H19"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="K30:L36"/>
-    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M29:R29"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="M30:R36"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="L25:S25"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="L24:R24"/>
-    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="I4:S4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="J18:K18"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L23:R23"/>
-    <mergeCell ref="A30:G36"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="H30:J36"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="L20:R20"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0" footer="0"/>
@@ -5177,7 +5699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5197,7 +5719,8 @@
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
     <col width="7.5" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5251,6 +5774,7 @@
         </is>
       </c>
       <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -5283,6 +5807,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5311,6 +5836,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -5369,6 +5895,12 @@
         </is>
       </c>
       <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>CONTINUA
+A PEÇA Nº</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
@@ -5441,10 +5973,11 @@
       </c>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
     </row>
     <row r="6" ht="21" customHeight="1">
       <c r="A6" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -5462,11 +5995,12 @@
       <c r="O6" s="17" t="n"/>
       <c r="P6" s="17" t="n"/>
       <c r="Q6" s="18" t="n"/>
-      <c r="R6" s="19" t="n"/>
+      <c r="R6" s="7" t="n"/>
+      <c r="S6" s="19" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -5484,11 +6018,12 @@
       <c r="O7" s="17" t="n"/>
       <c r="P7" s="17" t="n"/>
       <c r="Q7" s="18" t="n"/>
-      <c r="R7" s="19" t="n"/>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="19" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -5506,11 +6041,12 @@
       <c r="O8" s="17" t="n"/>
       <c r="P8" s="17" t="n"/>
       <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="19" t="n"/>
+      <c r="R8" s="7" t="n"/>
+      <c r="S8" s="19" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
@@ -5528,11 +6064,12 @@
       <c r="O9" s="17" t="n"/>
       <c r="P9" s="17" t="n"/>
       <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="19" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="19" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -5550,11 +6087,12 @@
       <c r="O10" s="17" t="n"/>
       <c r="P10" s="17" t="n"/>
       <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="19" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="19" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -5572,11 +6110,12 @@
       <c r="O11" s="17" t="n"/>
       <c r="P11" s="17" t="n"/>
       <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="19" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="19" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -5594,11 +6133,12 @@
       <c r="O12" s="17" t="n"/>
       <c r="P12" s="17" t="n"/>
       <c r="Q12" s="18" t="n"/>
-      <c r="R12" s="19" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="19" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -5616,11 +6156,12 @@
       <c r="O13" s="17" t="n"/>
       <c r="P13" s="17" t="n"/>
       <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="19" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="19" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -5638,11 +6179,12 @@
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
       <c r="Q14" s="18" t="n"/>
-      <c r="R14" s="19" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="19" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -5660,11 +6202,12 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="17" t="n"/>
       <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="19" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="19" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -5682,11 +6225,12 @@
       <c r="O16" s="17" t="n"/>
       <c r="P16" s="17" t="n"/>
       <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="19" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="19" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -5704,120 +6248,124 @@
       <c r="O17" s="17" t="n"/>
       <c r="P17" s="17" t="n"/>
       <c r="Q17" s="18" t="n"/>
-      <c r="R17" s="19" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="17" t="n"/>
+      <c r="P18" s="17" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2. PARADAS (continuação)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Nº da peça que estava na máquina, ou “—”</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Nº DA
-PEÇA
-(ou —)</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>CHAPA</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>INÍCIO</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>FIM</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>TURNO</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>MOTIVO
-(código 1–11)</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO DA PARADA</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="S19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Nº DA
+PEÇA
+(ou —)</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>CHAPA</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>INÍCIO</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="17" t="n"/>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>FIM</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>TURNO</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>MOTIVO
+(código 1–11)</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="19" t="n"/>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>DESCRIÇÃO DA PARADA</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -5836,10 +6384,11 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -5858,10 +6407,11 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -5880,10 +6430,11 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B24" s="7" t="n"/>
       <c r="C24" s="7" t="n"/>
@@ -5902,10 +6453,11 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
@@ -5924,10 +6476,11 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="n"/>
@@ -5946,10 +6499,11 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="n"/>
@@ -5968,10 +6522,11 @@
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
@@ -5990,10 +6545,11 @@
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
@@ -6012,276 +6568,332 @@
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>FECHAMENTO DA FOLHA (contramestre)</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="17" t="n"/>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>PEÇAS</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
       <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="20" t="inlineStr">
-        <is>
-          <t>LEMBRETE</t>
-        </is>
-      </c>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>Horas produzindo (soma dos trechos)</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="24">
-        <f>SUMPRODUCT(('Exemplo (frente)'!G7:G17&lt;&gt;"")*MOD('Exemplo (frente)'!G7:G17-'Exemplo (frente)'!F7:F17,1))+SUMPRODUCT(('Exemplo (frente)'!J7:J17&lt;&gt;"")*MOD('Exemplo (frente)'!J7:J17-'Exemplo (frente)'!I7:I17,1))+SUMPRODUCT(('Exemplo (frente)'!M7:M17&lt;&gt;"")*MOD('Exemplo (frente)'!M7:M17-'Exemplo (frente)'!L7:L17,1))+SUMPRODUCT(('Exemplo (frente)'!P7:P17&lt;&gt;"")*MOD('Exemplo (frente)'!P7:P17-'Exemplo (frente)'!O7:O17,1))+SUMPRODUCT(('Exemplo (verso)'!G6:G17&lt;&gt;"")*MOD('Exemplo (verso)'!G6:G17-'Exemplo (verso)'!F6:F17,1))+SUMPRODUCT(('Exemplo (verso)'!J6:J17&lt;&gt;"")*MOD('Exemplo (verso)'!J6:J17-'Exemplo (verso)'!I6:I17,1))+SUMPRODUCT(('Exemplo (verso)'!M6:M17&lt;&gt;"")*MOD('Exemplo (verso)'!M6:M17-'Exemplo (verso)'!L6:L17,1))+SUMPRODUCT(('Exemplo (verso)'!P6:P17&lt;&gt;"")*MOD('Exemplo (verso)'!P6:P17-'Exemplo (verso)'!O6:O17,1))</f>
-        <v/>
-      </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="23" t="inlineStr">
-        <is>
-          <t>Peças prontas (nº de ✓)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="18">
-        <f>COUNTA('Exemplo (frente)'!Q7:Q17)+COUNTA('Exemplo (verso)'!Q6:Q17)</f>
-        <v/>
-      </c>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Trecho é só produção.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> Parou? Feche o trecho e anote a parada com o </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Nº da peça</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve">. Voltou? </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>Próximo trecho da mesma linha</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t>. ✓ quando a peça ficar pronta.</t>
-          </r>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>Horas paradas (soma do quadro 2)</t>
+      <c r="S31" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>FECHAMENTO DA FOLHA (contramestre)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
-      <c r="E33" s="24">
-        <f>SUMPRODUCT(('Exemplo (frente)'!G20:G27&lt;&gt;"")*MOD('Exemplo (frente)'!G20:G27-'Exemplo (frente)'!E20:E27,1))+SUMPRODUCT(('Exemplo (verso)'!G20:G29&lt;&gt;"")*MOD('Exemplo (verso)'!G20:G29-'Exemplo (verso)'!E20:E29,1))</f>
-        <v/>
-      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t>Continuam na próxima folha</t>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>PEÇAS</t>
         </is>
       </c>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
-      <c r="K33" s="18">
-        <f>SUMPRODUCT(('Exemplo (frente)'!C7:C17&lt;&gt;"")*('Exemplo (frente)'!Q7:Q17=""))+SUMPRODUCT(('Exemplo (verso)'!C6:C17&lt;&gt;"")*('Exemplo (verso)'!Q6:Q17=""))</f>
-        <v/>
-      </c>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>LEMBRETE</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Total (24 h no dia, ou as horas dos turnos)</t>
+          <t>Horas produzindo (soma dos trechos)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="24">
-        <f>E32+E33</f>
+        <f>SUMPRODUCT(('Exemplo (frente)'!G7:G16&lt;&gt;"")*MOD('Exemplo (frente)'!G7:G16-'Exemplo (frente)'!F7:F16,1))+SUMPRODUCT(('Exemplo (frente)'!J7:J16&lt;&gt;"")*MOD('Exemplo (frente)'!J7:J16-'Exemplo (frente)'!I7:I16,1))+SUMPRODUCT(('Exemplo (frente)'!M7:M16&lt;&gt;"")*MOD('Exemplo (frente)'!M7:M16-'Exemplo (frente)'!L7:L16,1))+SUMPRODUCT(('Exemplo (frente)'!P7:P16&lt;&gt;"")*MOD('Exemplo (frente)'!P7:P16-'Exemplo (frente)'!O7:O16,1))+SUMPRODUCT(('Exemplo (verso)'!G6:G18&lt;&gt;"")*MOD('Exemplo (verso)'!G6:G18-'Exemplo (verso)'!F6:F18,1))+SUMPRODUCT(('Exemplo (verso)'!J6:J18&lt;&gt;"")*MOD('Exemplo (verso)'!J6:J18-'Exemplo (verso)'!I6:I18,1))+SUMPRODUCT(('Exemplo (verso)'!M6:M18&lt;&gt;"")*MOD('Exemplo (verso)'!M6:M18-'Exemplo (verso)'!L6:L18,1))+SUMPRODUCT(('Exemplo (verso)'!P6:P18&lt;&gt;"")*MOD('Exemplo (verso)'!P6:P18-'Exemplo (verso)'!O6:O18,1))</f>
         <v/>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>Conferido por (chapa)</t>
+          <t>Peças prontas (nº de ✓)</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
-      <c r="K34" s="18" t="n"/>
+      <c r="K34" s="18">
+        <f>COUNTA('Exemplo (frente)'!Q7:Q16)+COUNTA('Exemplo (verso)'!Q6:Q18)</f>
+        <v/>
+      </c>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Trecho é só produção.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Parou? Feche o trecho e anote a parada com o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Nº da peça</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">. Voltou? </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>Próximo trecho da mesma linha</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>. ✓ quando a peça ficar pronta.</t>
+          </r>
+        </is>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="21" customHeight="1"/>
-    <row r="36" ht="21" customHeight="1"/>
+      <c r="S34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Horas paradas (soma do quadro 2)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="24">
+        <f>SUMPRODUCT(('Exemplo (frente)'!G19:G29&lt;&gt;"")*MOD('Exemplo (frente)'!G19:G29-'Exemplo (frente)'!E19:E29,1))+SUMPRODUCT(('Exemplo (verso)'!G21:G31&lt;&gt;"")*MOD('Exemplo (verso)'!G21:G31-'Exemplo (verso)'!E21:E31,1))</f>
+        <v/>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>Continuam na próxima folha</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="18">
+        <f>SUMPRODUCT(('Exemplo (frente)'!C7:C16&lt;&gt;"")*('Exemplo (frente)'!Q7:Q16=""))+SUMPRODUCT(('Exemplo (verso)'!C6:C18&lt;&gt;"")*('Exemplo (verso)'!Q6:Q18=""))</f>
+        <v/>
+      </c>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Total (24 h no dia, ou as horas dos turnos)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="24">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>Conferido por (chapa)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1"/>
+    <row r="38" ht="21" customHeight="1"/>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="86">
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="M33:S33"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="L21:R21"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="M31:R31"/>
+    <mergeCell ref="K35:L35"/>
     <mergeCell ref="A1:L2"/>
     <mergeCell ref="O1:P1"/>
+    <mergeCell ref="L24:S24"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="L26:S26"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="J31:K31"/>
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="J21:K21"/>
-    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="E35:G35"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="L27:S27"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L20:R20"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="L22:R22"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="H31:L31"/>
-    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="L28:S28"/>
     <mergeCell ref="J27:K27"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="L23:S23"/>
     <mergeCell ref="J20:K20"/>
-    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="K4:M4"/>
+    <mergeCell ref="M34:S36"/>
+    <mergeCell ref="H35:J35"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="L24:R24"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="E33:G33"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="H4:J4"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="I3:R3"/>
-    <mergeCell ref="L25:R25"/>
+    <mergeCell ref="I19:S19"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="E36:G36"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="J24:K24"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L28:R28"/>
+    <mergeCell ref="L30:S30"/>
+    <mergeCell ref="L20:S20"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="L29:S29"/>
     <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L23:R23"/>
+    <mergeCell ref="L22:S22"/>
+    <mergeCell ref="L31:S31"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="L21:S21"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H33:L33"/>
     <mergeCell ref="H34:J34"/>
-    <mergeCell ref="A32:D32"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="R4:R5"/>
+    <mergeCell ref="H36:J36"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="J30:K30"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="G28:H28"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="M32:R34"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="I3:S3"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="L25:S25"/>
+    <mergeCell ref="S4:S5"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/docs/folha-modelo/diario-de-bordo-v3.xlsx
+++ b/docs/folha-modelo/diario-de-bordo-v3.xlsx
@@ -633,9 +633,9 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
-    <col width="7.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -838,8 +838,9 @@
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="11" t="inlineStr">
         <is>
-          <t>PEÇA
-PRONTA ✓</t>
+          <t>PRONTA:
+TURNO QUE
+FINALIZOU</t>
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr">
@@ -854,7 +855,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
@@ -1701,7 +1702,7 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">6. Marque </t>
+            <t xml:space="preserve">6. </t>
           </r>
           <r>
             <rPr>
@@ -1710,15 +1711,49 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t>✓ PRONTA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> quando a peça terminar. Não terminou? Deixe em branco e continue na próxima folha.
+            <t>Peça pronta?</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Escreva em </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>PRONTA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>turno que finalizou</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> (1, 2 ou 3). Não terminou? Deixe em branco e continue na próxima folha.
 </t>
           </r>
           <r>
@@ -1778,7 +1813,7 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve"> o número da linha de cima. ✓ só na última linha.</t>
+            <t xml:space="preserve"> o número da linha de cima. O turno em PRONTA vai só na última linha.</t>
           </r>
         </is>
       </c>
@@ -2012,7 +2047,7 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · ✓
+            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · Pronta: 1
 </t>
           </r>
           <r>
@@ -2320,9 +2355,9 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
-    <col width="7.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2480,8 +2515,9 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="11" t="inlineStr">
         <is>
-          <t>PEÇA
-PRONTA ✓</t>
+          <t>PRONTA:
+TURNO QUE
+FINALIZOU</t>
         </is>
       </c>
       <c r="R4" s="11" t="inlineStr">
@@ -2496,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
@@ -3256,7 +3292,7 @@
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>Peças prontas (nº de ✓)</t>
+          <t>Peças prontas (turno em PRONTA)</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
@@ -3317,7 +3353,24 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t>. ✓ quando a peça ficar pronta.</t>
+            <t xml:space="preserve">. Peça pronta: o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>turno que finalizou</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> em PRONTA.</t>
           </r>
         </is>
       </c>
@@ -3517,9 +3570,9 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
-    <col width="7.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3730,8 +3783,9 @@
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="11" t="inlineStr">
         <is>
-          <t>PEÇA
-PRONTA ✓</t>
+          <t>PRONTA:
+TURNO QUE
+FINALIZOU</t>
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr">
@@ -3746,7 +3800,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
@@ -3854,10 +3908,8 @@
       <c r="N7" s="16" t="n"/>
       <c r="O7" s="17" t="n"/>
       <c r="P7" s="17" t="n"/>
-      <c r="Q7" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="R7" s="7" t="n"/>
       <c r="S7" s="19" t="n"/>
@@ -3909,10 +3961,8 @@
       <c r="N8" s="16" t="n"/>
       <c r="O8" s="17" t="n"/>
       <c r="P8" s="17" t="n"/>
-      <c r="Q8" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q8" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="R8" s="7" t="n"/>
       <c r="S8" s="19" t="n"/>
@@ -3956,10 +4006,8 @@
       <c r="N9" s="16" t="n"/>
       <c r="O9" s="17" t="n"/>
       <c r="P9" s="17" t="n"/>
-      <c r="Q9" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q9" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="R9" s="7" t="n"/>
       <c r="S9" s="19" t="n"/>
@@ -4011,10 +4059,8 @@
       <c r="N10" s="16" t="n"/>
       <c r="O10" s="17" t="n"/>
       <c r="P10" s="17" t="n"/>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="7" t="n"/>
       <c r="S10" s="19" t="inlineStr">
@@ -4133,10 +4179,8 @@
       <c r="N12" s="16" t="n"/>
       <c r="O12" s="17" t="n"/>
       <c r="P12" s="17" t="n"/>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q12" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="R12" s="7" t="n">
         <v>5</v>
@@ -4186,10 +4230,8 @@
       <c r="N13" s="16" t="n"/>
       <c r="O13" s="17" t="n"/>
       <c r="P13" s="17" t="n"/>
-      <c r="Q13" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="R13" s="7" t="n"/>
       <c r="S13" s="19" t="n"/>
@@ -4233,10 +4275,8 @@
       <c r="N14" s="16" t="n"/>
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q14" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="R14" s="7" t="n"/>
       <c r="S14" s="19" t="n"/>
@@ -5099,7 +5139,7 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">6. Marque </t>
+            <t xml:space="preserve">6. </t>
           </r>
           <r>
             <rPr>
@@ -5108,15 +5148,49 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t>✓ PRONTA</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="FF111111"/>
-              <sz val="8.5"/>
-            </rPr>
-            <t xml:space="preserve"> quando a peça terminar. Não terminou? Deixe em branco e continue na próxima folha.
+            <t>Peça pronta?</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> Escreva em </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>PRONTA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>turno que finalizou</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> (1, 2 ou 3). Não terminou? Deixe em branco e continue na próxima folha.
 </t>
           </r>
           <r>
@@ -5176,7 +5250,7 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve"> o número da linha de cima. ✓ só na última linha.</t>
+            <t xml:space="preserve"> o número da linha de cima. O turno em PRONTA vai só na última linha.</t>
           </r>
         </is>
       </c>
@@ -5410,7 +5484,7 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · ✓
+            <t xml:space="preserve">VIGA · D51 · Trecho 1: 13:00–14:30 · Trecho 2: 15:30–17:00 · Pronta: 1
 </t>
           </r>
           <r>
@@ -5718,9 +5792,9 @@
     <col width="7" customWidth="1" min="14" max="14"/>
     <col width="6.6" customWidth="1" min="15" max="15"/>
     <col width="6.6" customWidth="1" min="16" max="16"/>
-    <col width="7.5" customWidth="1" min="17" max="17"/>
+    <col width="9.5" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5890,8 +5964,9 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="11" t="inlineStr">
         <is>
-          <t>PEÇA
-PRONTA ✓</t>
+          <t>PRONTA:
+TURNO QUE
+FINALIZOU</t>
         </is>
       </c>
       <c r="R4" s="11" t="inlineStr">
@@ -5906,7 +5981,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
@@ -6666,7 +6741,7 @@
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>Peças prontas (nº de ✓)</t>
+          <t>Peças prontas (turno em PRONTA)</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
@@ -6727,7 +6802,24 @@
               <color rgb="FF111111"/>
               <sz val="8.5"/>
             </rPr>
-            <t>. ✓ quando a peça ficar pronta.</t>
+            <t xml:space="preserve">. Peça pronta: o </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>turno que finalizou</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF111111"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve"> em PRONTA.</t>
           </r>
         </is>
       </c>
